--- a/Script.xlsx
+++ b/Script.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tde\Desktop\College\PsycoPy\Paige Program Version 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tde\Desktop\College\PsycoPy\Alysa Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C32DF3F-7BD1-445B-99AE-F52EDB2E7A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E03238-DDC0-46EC-AAF8-9C6329F88227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,42 +96,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Order</t>
   </si>
   <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Comission_Integrity</t>
-  </si>
-  <si>
-    <t>Omission_Integrity</t>
-  </si>
-  <si>
-    <t>Reinforcement_Schedule</t>
-  </si>
-  <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>Reinforcement_Variable</t>
-  </si>
-  <si>
-    <t>BL</t>
-  </si>
-  <si>
-    <t>FI</t>
-  </si>
-  <si>
-    <t>Intervention</t>
-  </si>
-  <si>
-    <t>DRO</t>
-  </si>
-  <si>
-    <t>ComINT</t>
+    <t>PhaseName</t>
+  </si>
+  <si>
+    <t>Reset_PointsTF</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>DRO80100</t>
+  </si>
+  <si>
+    <t>Button_1</t>
+  </si>
+  <si>
+    <t>Button_2</t>
+  </si>
+  <si>
+    <t>Button_3</t>
+  </si>
+  <si>
+    <t>Button_4</t>
+  </si>
+  <si>
+    <t>Button_5</t>
+  </si>
+  <si>
+    <t>1 2</t>
+  </si>
+  <si>
+    <t>BackgroundColor</t>
   </si>
 </sst>
 </file>
@@ -525,150 +531,141 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultColWidth="20.7265625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>100</v>
-      </c>
-      <c r="E2">
-        <v>40</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>80</v>
-      </c>
-      <c r="D4">
-        <v>80</v>
-      </c>
-      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>100</v>
       </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="L4" s="1"/>
-    </row>
-    <row r="5" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L5" s="1"/>
-    </row>
-    <row r="6" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L6" s="1"/>
-    </row>
-    <row r="7" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L7" s="1"/>
-    </row>
-    <row r="8" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L8" s="1"/>
-    </row>
-    <row r="9" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L10" s="1"/>
-    </row>
-    <row r="11" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L11" s="1"/>
-    </row>
-    <row r="12" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L13" s="1"/>
-    </row>
-    <row r="14" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L15" s="1"/>
-    </row>
-    <row r="22" spans="11:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="11:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="11:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="K24" s="1"/>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N15" s="1"/>
+    </row>
+    <row r="22" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M22" s="1"/>
+    </row>
+    <row r="23" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M23" s="1"/>
+    </row>
+    <row r="24" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M24" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -683,21 +680,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9F5CAB0486A994CA2C3B13E059EF2AE" ma:contentTypeVersion="0" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8645ec4a60d0c8c7009d2d6675847a91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636d7205651659ec4fcda0bcbde9384b">
     <xsd:element name="properties">
@@ -811,15 +799,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -834,7 +823,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -848,4 +837,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Script.xlsx
+++ b/Script.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tde\Desktop\College\PsycoPy\Alysa Program\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tommy.Artichoke\Desktop\Masters\PsychoPy\5 buttons\DRO-Experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E03238-DDC0-46EC-AAF8-9C6329F88227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E87E124-28B3-43F3-BBD0-4F01BFCB6B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26760" yWindow="3750" windowWidth="28800" windowHeight="15375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -91,12 +91,38 @@
         </r>
       </text>
     </comment>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{67B8D2F8-06E4-4320-BD2F-6263D7666945}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Calibri Light"/>
+            <family val="2"/>
+            <scheme val="major"/>
+          </rPr>
+          <t xml:space="preserve">Values
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Calibri Light"/>
+            <family val="2"/>
+            <scheme val="major"/>
+          </rPr>
+          <t>Each iteration of this loop, a different one of these values will be chosen. This will be the value of the variable named above.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>Order</t>
   </si>
@@ -110,41 +136,35 @@
     <t>Reset_PointsTF</t>
   </si>
   <si>
-    <t>Assessment</t>
+    <t>Button_1</t>
+  </si>
+  <si>
+    <t>Button_2</t>
+  </si>
+  <si>
+    <t>Button_3</t>
+  </si>
+  <si>
+    <t>Button_4</t>
+  </si>
+  <si>
+    <t>Button_5</t>
+  </si>
+  <si>
+    <t>BackgroundColor</t>
+  </si>
+  <si>
+    <t>Skippable_BreakTF</t>
   </si>
   <si>
     <t>Break</t>
-  </si>
-  <si>
-    <t>DRO80100</t>
-  </si>
-  <si>
-    <t>Button_1</t>
-  </si>
-  <si>
-    <t>Button_2</t>
-  </si>
-  <si>
-    <t>Button_3</t>
-  </si>
-  <si>
-    <t>Button_4</t>
-  </si>
-  <si>
-    <t>Button_5</t>
-  </si>
-  <si>
-    <t>1 2</t>
-  </si>
-  <si>
-    <t>BackgroundColor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +195,12 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -202,13 +228,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,9 +561,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultColWidth="20.7265625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="20.81640625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.7265625" style="1"/>
+    <col min="1" max="1" width="20.81640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="2" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -545,19 +574,19 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>1</v>
@@ -566,7 +595,10 @@
         <v>3</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -574,19 +606,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I2" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -594,13 +626,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
       </c>
       <c r="N3" s="1"/>
     </row>
@@ -609,20 +644,17 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -656,15 +688,25 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K15" s="3"/>
       <c r="N15" s="1"/>
     </row>
-    <row r="22" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="11:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" spans="11:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K18" s="3"/>
+    </row>
+    <row r="22" spans="11:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="11:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="M23" s="1"/>
     </row>
-    <row r="24" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="11:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="M24" s="1"/>
     </row>
   </sheetData>
@@ -674,7 +716,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -686,6 +728,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9F5CAB0486A994CA2C3B13E059EF2AE" ma:contentTypeVersion="0" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8645ec4a60d0c8c7009d2d6675847a91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636d7205651659ec4fcda0bcbde9384b">
     <xsd:element name="properties">
@@ -799,15 +850,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
   <ds:schemaRefs>
@@ -824,6 +866,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -837,12 +887,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>